--- a/base/StructureDefinition-SGValueSet.xlsx
+++ b/base/StructureDefinition-SGValueSet.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3281" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3391" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}vsd-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}vsd-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -456,6 +456,10 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
+    <t>ele-1
+shr-1</t>
+  </si>
+  <si>
     <t>ValueSet.extension:versionAlgorithm</t>
   </si>
   <si>
@@ -475,6 +479,10 @@
     <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>ValueSet.extension:versionPolicy</t>
   </si>
   <si>
@@ -491,23 +499,74 @@
     <t>Defines the versioning policy of the artifact.</t>
   </si>
   <si>
-    <t>ValueSet.extension:authoritativeSource</t>
-  </si>
-  <si>
-    <t>authoritativeSource</t>
+    <t>ValueSet.extension:valueSetAuthoritativeSource</t>
+  </si>
+  <si>
+    <t>valueSetAuthoritativeSource</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {valueset-authoritativeSource}
 </t>
   </si>
   <si>
-    <t>Reference to the current trusted source of the ValueSet resource (metadata and definition)</t>
-  </si>
-  <si>
-    <t>A reference to the authoritative accessible, persisted source of truth of the entire Value Set Definition, including textual information and available versions.</t>
+    <t>DEPRECATED: Use artifact-authoritativeSource</t>
   </si>
   <si>
     <t>If this extension is not present, then the canonical URL (ValueSet.url) also serves the purpose of specifying the authoritative source.  A difference between the canonical URL and the authoritiative source might arise in some cases due to ongoing organization restructuring, etc., and in those cases this extension may be used.  The URL of the authoritative source is intended to be resolvable but that cannot be guaranteed. The designated "authoritative source" is normally expected to be able to generate a valid expansion of the value set, and if for some reason it cannot then the valueset-trusted-expansion should be used.</t>
+  </si>
+  <si>
+    <t>ValueSet.extension:authoritativeSource</t>
+  </si>
+  <si>
+    <t>authoritativeSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {artifact-authoritativeSource}
+</t>
+  </si>
+  <si>
+    <t>Original definitions</t>
+  </si>
+  <si>
+    <t>A reference to the offical/source of truth definition of the content, typically outside the FHIR ecosystem. For example, the authoritativeSource for a ValueSet might be a spreadsheet published on an agency website.</t>
+  </si>
+  <si>
+    <t>Note that this concept is different from web-source (where the page for the content can be found it is different from the canonical), and package-source (what package the resource came from). This is an abbreviated way of saying something that could be expressed with Provenance. This extensions points to the content, not the authority for the content.</t>
+  </si>
+  <si>
+    <t>ValueSet.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
+  </si>
+  <si>
+    <t>ValueSet.extension:workflowStatusDescription</t>
+  </si>
+  <si>
+    <t>workflowStatusDescription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {valueset-workflowStatusDescription}
+</t>
+  </si>
+  <si>
+    <t>Content authoring workflow status</t>
+  </si>
+  <si>
+    <t>Indicates a specific phase or activity status for the value set. Different stewards have different processes for managing content.</t>
+  </si>
+  <si>
+    <t>This element can be used to communicate additional status beyond the publication status for the artifact, including concepts such as deprecated. Note that for _deprecated_ specifically, the artifact status must be `active` since the artifact is still supported for use.</t>
   </si>
   <si>
     <t>ValueSet.modifierExtension</t>
@@ -822,7 +881,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -1127,7 +1186,7 @@
     <t>Details of how a designation would be used.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/designation-use</t>
+    <t>http://hl7.org/fhir/ValueSet/designation-use|4.0.1</t>
   </si>
   <si>
     <t>ValueSet.compose.include.concept.designation.value</t>
@@ -1202,7 +1261,7 @@
     <t>ValueSet.compose.include.valueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet)
+    <t xml:space="preserve">canonical(ValueSet|4.0.1)
 </t>
   </si>
   <si>
@@ -1788,20 +1847,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN90"/>
+  <dimension ref="A1:AN93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.23046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.23046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.91015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="52.91015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.55859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="39.375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1810,26 +1869,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="62.08984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.51953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="52.0078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.70703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="41.1171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.98046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.67578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2858,7 +2917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>136</v>
       </c>
@@ -2954,7 +3013,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>135</v>
@@ -2972,15 +3031,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -3002,16 +3061,16 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3070,7 +3129,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>135</v>
@@ -3090,13 +3149,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -3109,7 +3168,7 @@
         <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -3118,13 +3177,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3184,7 +3243,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>135</v>
@@ -3204,13 +3263,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3223,7 +3282,7 @@
         <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>20</v>
@@ -3232,16 +3291,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3300,7 +3359,7 @@
         <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>135</v>
@@ -3318,48 +3377,48 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3407,7 +3466,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3416,13 +3475,13 @@
         <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -3434,20 +3493,22 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>77</v>
@@ -3459,23 +3520,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O15" t="s" s="2">
         <v>169</v>
       </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3523,28 +3580,28 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3552,12 +3609,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3566,7 +3625,7 @@
         <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3575,23 +3634,21 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3639,7 +3696,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3648,64 +3705,66 @@
         <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I17" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3753,39 +3812,39 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3808,19 +3867,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>181</v>
+        <v>99</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3869,7 +3928,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3878,19 +3937,19 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -3898,10 +3957,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3909,13 +3968,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
@@ -3924,18 +3983,20 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3983,13 +4044,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4001,16 +4062,16 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>198</v>
       </c>
@@ -4032,22 +4093,22 @@
         <v>86</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4073,13 +4134,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4100,7 +4161,7 @@
         <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>77</v>
@@ -4115,21 +4176,21 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4152,19 +4213,19 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4213,7 +4274,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4222,7 +4283,7 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>97</v>
@@ -4231,35 +4292,35 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -4268,16 +4329,16 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4327,7 +4388,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4342,24 +4403,24 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4376,26 +4437,24 @@
         <v>86</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4419,13 +4478,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4443,10 +4502,10 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>77</v>
@@ -4461,21 +4520,21 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4483,13 +4542,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -4498,18 +4557,20 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4557,13 +4618,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4575,10 +4636,10 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4586,42 +4647,42 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4671,7 +4732,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4689,21 +4750,21 @@
         <v>84</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4711,13 +4772,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4726,19 +4787,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4787,13 +4848,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4805,10 +4866,10 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4816,10 +4877,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4842,16 +4903,16 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4877,13 +4938,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4901,7 +4962,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4919,7 +4980,7 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4928,44 +4989,44 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5015,7 +5076,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5030,10 +5091,10 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -5044,10 +5105,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5058,7 +5119,7 @@
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5067,21 +5128,23 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5129,13 +5192,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5150,29 +5213,29 @@
         <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5181,23 +5244,21 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>274</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5221,13 +5282,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5245,13 +5306,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -5263,25 +5324,25 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5297,18 +5358,20 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5357,7 +5420,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5412,7 +5475,7 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>282</v>
@@ -5420,7 +5483,9 @@
       <c r="M32" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="N32" s="2"/>
+      <c r="N32" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5469,7 +5534,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5481,38 +5546,38 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>286</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>159</v>
+        <v>288</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5524,18 +5589,20 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5583,75 +5650,71 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5705,16 +5768,16 @@
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -5728,10 +5791,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5751,20 +5814,18 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>296</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5813,7 +5874,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5825,16 +5886,16 @@
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5842,21 +5903,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5865,19 +5926,19 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>304</v>
+        <v>180</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5927,22 +5988,22 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -5956,18 +6017,18 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>82</v>
@@ -5976,24 +6037,26 @@
         <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6041,10 +6104,10 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>82</v>
@@ -6053,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>309</v>
+        <v>135</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6070,10 +6133,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6093,18 +6156,20 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>181</v>
+        <v>314</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6153,7 +6218,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6165,16 +6230,16 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6182,21 +6247,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6205,19 +6270,19 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>129</v>
+        <v>226</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>162</v>
+        <v>322</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6267,22 +6332,22 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6296,18 +6361,18 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>82</v>
@@ -6316,26 +6381,24 @@
         <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6383,10 +6446,10 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
@@ -6395,7 +6458,7 @@
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>135</v>
+        <v>327</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -6412,10 +6475,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6435,20 +6498,18 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6497,7 +6558,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6506,13 +6567,13 @@
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6526,21 +6587,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6549,19 +6610,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>321</v>
+        <v>180</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6611,22 +6672,22 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6640,14 +6701,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6660,24 +6721,26 @@
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6725,7 +6788,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6734,10 +6797,10 @@
         <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -6754,10 +6817,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6777,18 +6840,20 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>181</v>
+        <v>99</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>282</v>
+        <v>332</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6837,7 +6902,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6846,13 +6911,13 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
@@ -6866,21 +6931,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6889,19 +6954,19 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>287</v>
+        <v>337</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6951,22 +7016,22 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -6980,14 +7045,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7000,26 +7065,24 @@
         <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>292</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>293</v>
+        <v>342</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7067,7 +7130,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7076,10 +7139,10 @@
         <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -7096,10 +7159,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7107,7 +7170,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>77</v>
@@ -7122,17 +7185,15 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7181,10 +7242,10 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>77</v>
@@ -7193,10 +7254,10 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
@@ -7210,21 +7271,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7236,16 +7297,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7295,22 +7356,22 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
@@ -7324,14 +7385,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7344,24 +7405,26 @@
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7409,7 +7472,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7421,10 +7484,10 @@
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7438,10 +7501,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7449,7 +7512,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>77</v>
@@ -7464,15 +7527,17 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>282</v>
+        <v>349</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7521,10 +7586,10 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>77</v>
@@ -7533,10 +7598,10 @@
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7550,21 +7615,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7576,16 +7641,16 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>288</v>
+        <v>354</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7635,22 +7700,22 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>289</v>
+        <v>352</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
@@ -7664,14 +7729,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7684,26 +7749,24 @@
         <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>293</v>
+        <v>358</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7751,7 +7814,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>294</v>
+        <v>356</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7763,10 +7826,10 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>20</v>
@@ -7780,10 +7843,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7806,17 +7869,15 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7841,13 +7902,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -7865,7 +7926,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>345</v>
+        <v>302</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7877,10 +7938,10 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>20</v>
@@ -7894,21 +7955,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7920,16 +7981,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>350</v>
+        <v>129</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>352</v>
+        <v>306</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>353</v>
+        <v>180</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7955,13 +8016,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7979,22 +8040,22 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>349</v>
+        <v>307</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>20</v>
@@ -8008,42 +8069,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
@@ -8091,22 +8156,22 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8120,10 +8185,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8134,7 +8199,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8143,19 +8208,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>278</v>
+        <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8181,13 +8246,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8205,22 +8270,22 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
@@ -8234,10 +8299,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8260,15 +8325,17 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>181</v>
+        <v>368</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>282</v>
+        <v>369</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8293,13 +8360,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8317,7 +8384,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>284</v>
+        <v>367</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8329,10 +8396,10 @@
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>20</v>
@@ -8346,21 +8413,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8372,17 +8439,15 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>287</v>
+        <v>375</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8431,22 +8496,22 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>289</v>
+        <v>374</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>20</v>
@@ -8460,14 +8525,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8480,26 +8545,24 @@
         <v>20</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>292</v>
+        <v>378</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>293</v>
+        <v>379</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8547,7 +8610,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>294</v>
+        <v>377</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8556,10 +8619,10 @@
         <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -8576,10 +8639,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8587,7 +8650,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>77</v>
@@ -8599,16 +8662,16 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>367</v>
+        <v>300</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>368</v>
+        <v>301</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8659,10 +8722,10 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>302</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>77</v>
@@ -8671,10 +8734,10 @@
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>20</v>
@@ -8688,21 +8751,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8711,19 +8774,19 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>370</v>
+        <v>305</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>371</v>
+        <v>306</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>372</v>
+        <v>180</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8749,13 +8812,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8773,22 +8836,22 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>20</v>
@@ -8802,44 +8865,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -8887,19 +8952,19 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>375</v>
+        <v>312</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
@@ -8916,10 +8981,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8927,10 +8992,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -8942,17 +9007,15 @@
         <v>86</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>380</v>
+        <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9001,16 +9064,16 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>97</v>
@@ -9030,10 +9093,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9041,10 +9104,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9053,19 +9116,19 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9091,13 +9154,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9115,16 +9178,16 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>97</v>
@@ -9144,10 +9207,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9155,7 +9218,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>77</v>
@@ -9167,19 +9230,19 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9229,10 +9292,10 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>77</v>
@@ -9244,7 +9307,7 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>20</v>
@@ -9258,10 +9321,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9272,7 +9335,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9281,18 +9344,20 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>181</v>
+        <v>398</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>282</v>
+        <v>399</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9341,22 +9406,22 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>284</v>
+        <v>397</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>20</v>
+        <v>402</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>20</v>
@@ -9370,14 +9435,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9396,16 +9461,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>287</v>
+        <v>404</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>288</v>
+        <v>405</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9455,7 +9520,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>289</v>
+        <v>403</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9464,13 +9529,13 @@
         <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>20</v>
@@ -9484,46 +9549,44 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>292</v>
+        <v>409</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>293</v>
+        <v>410</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>20</v>
       </c>
@@ -9571,22 +9634,22 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>294</v>
+        <v>408</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>20</v>
@@ -9600,10 +9663,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9626,17 +9689,15 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>398</v>
+        <v>300</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9685,7 +9746,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>397</v>
+        <v>302</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -9697,10 +9758,10 @@
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
@@ -9714,21 +9775,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9740,16 +9801,16 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>402</v>
+        <v>305</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>403</v>
+        <v>306</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>404</v>
+        <v>180</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9799,22 +9860,22 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>401</v>
+        <v>307</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>20</v>
@@ -9828,44 +9889,46 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>406</v>
+        <v>129</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>407</v>
+        <v>310</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>408</v>
+        <v>311</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
       </c>
@@ -9913,22 +9976,22 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>405</v>
+        <v>312</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>20</v>
@@ -9942,10 +10005,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9968,24 +10031,22 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>406</v>
+        <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q72" t="s" s="2">
-        <v>414</v>
-      </c>
+      <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
         <v>20</v>
       </c>
@@ -10029,7 +10090,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10058,10 +10119,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10069,10 +10130,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10084,16 +10145,16 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10143,13 +10204,13 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
@@ -10172,10 +10233,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10198,15 +10259,17 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>181</v>
+        <v>424</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>282</v>
+        <v>425</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10255,7 +10318,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>284</v>
+        <v>423</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10267,10 +10330,10 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>20</v>
@@ -10284,21 +10347,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -10310,22 +10373,24 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>129</v>
+        <v>424</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>287</v>
+        <v>429</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>288</v>
+        <v>430</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>162</v>
+        <v>431</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q75" s="2"/>
+      <c r="Q75" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="R75" t="s" s="2">
         <v>20</v>
       </c>
@@ -10369,22 +10434,22 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>289</v>
+        <v>428</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>20</v>
@@ -10398,14 +10463,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10418,26 +10483,24 @@
         <v>20</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>292</v>
+        <v>434</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>293</v>
+        <v>435</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>20</v>
       </c>
@@ -10485,7 +10548,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>294</v>
+        <v>433</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -10497,10 +10560,10 @@
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>20</v>
@@ -10514,10 +10577,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10525,7 +10588,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>77</v>
@@ -10540,17 +10603,15 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>423</v>
+        <v>300</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -10599,10 +10660,10 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>422</v>
+        <v>302</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>77</v>
@@ -10611,10 +10672,10 @@
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>20</v>
@@ -10628,21 +10689,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -10654,15 +10715,17 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>427</v>
+        <v>129</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>428</v>
+        <v>305</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -10711,22 +10774,22 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>426</v>
+        <v>307</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
@@ -10740,14 +10803,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10760,22 +10823,26 @@
         <v>20</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>431</v>
+        <v>310</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
       </c>
@@ -10823,7 +10890,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>430</v>
+        <v>312</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -10835,10 +10902,10 @@
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>433</v>
+        <v>135</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>20</v>
@@ -10852,10 +10919,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10863,7 +10930,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>77</v>
@@ -10878,15 +10945,17 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>282</v>
+        <v>441</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -10935,10 +11004,10 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>284</v>
+        <v>440</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>77</v>
@@ -10947,10 +11016,10 @@
         <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>20</v>
@@ -10964,21 +11033,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -10990,17 +11059,15 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>129</v>
+        <v>445</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>287</v>
+        <v>446</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11049,22 +11116,22 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>289</v>
+        <v>444</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>20</v>
@@ -11078,14 +11145,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11098,26 +11165,22 @@
         <v>20</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>292</v>
+        <v>449</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>20</v>
       </c>
@@ -11165,7 +11228,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>294</v>
+        <v>448</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11177,10 +11240,10 @@
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>135</v>
+        <v>451</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>20</v>
@@ -11194,10 +11257,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11220,13 +11283,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>438</v>
+        <v>300</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>439</v>
+        <v>301</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11277,7 +11340,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>437</v>
+        <v>302</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -11289,10 +11352,10 @@
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>20</v>
@@ -11306,21 +11369,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -11332,24 +11395,22 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>441</v>
+        <v>305</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>442</v>
+        <v>306</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>443</v>
+        <v>180</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q84" t="s" s="2">
-        <v>444</v>
-      </c>
+      <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
         <v>20</v>
       </c>
@@ -11393,22 +11454,22 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>440</v>
+        <v>307</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>20</v>
@@ -11422,44 +11483,46 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>446</v>
+        <v>310</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>447</v>
+        <v>311</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
       </c>
@@ -11507,22 +11570,22 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>445</v>
+        <v>312</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
@@ -11536,10 +11599,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11562,17 +11625,15 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>181</v>
+        <v>99</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -11621,7 +11682,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -11650,10 +11711,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11676,20 +11737,24 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="R87" t="s" s="2">
         <v>20</v>
       </c>
@@ -11733,7 +11798,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -11742,7 +11807,7 @@
         <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>97</v>
@@ -11762,10 +11827,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11788,15 +11853,17 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -11845,7 +11912,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -11854,7 +11921,7 @@
         <v>77</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>97</v>
@@ -11874,10 +11941,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11888,7 +11955,7 @@
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>20</v>
@@ -11900,16 +11967,16 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11959,13 +12026,13 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>20</v>
@@ -11988,10 +12055,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12002,7 +12069,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -12014,17 +12081,15 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12073,16 +12138,16 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>20</v>
+        <v>474</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>97</v>
@@ -12100,18 +12165,358 @@
         <v>20</v>
       </c>
     </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN90">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AN93">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI89">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
